--- a/prix/lambris.xlsx
+++ b/prix/lambris.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lambris\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6E0D5E-A1AB-4E72-B3B7-CE390136D4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5695FF4E-335C-4787-BD41-E0D4453DAA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -635,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="21">
-        <v>100.86900000000659</v>
+        <v>71.39200000000659</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>6</v>
@@ -681,7 +681,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="21">
-        <v>78.721999999996953</v>
+        <v>32.041999999996946</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>19</v>
@@ -704,7 +704,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="21">
-        <v>82.419000000000437</v>
+        <v>42.287000000000432</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>20</v>
@@ -727,7 +727,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="21">
-        <v>93.057999999999993</v>
+        <v>69.795999999999992</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>21</v>

--- a/prix/lambris.xlsx
+++ b/prix/lambris.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lambris\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5695FF4E-335C-4787-BD41-E0D4453DAA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39095F01-1501-4B42-B16B-651DBE3A60A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -244,9 +244,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -628,13 +625,13 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="12">
         <v>15</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="20">
         <v>71.39200000000659</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -651,13 +648,13 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="12">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>125.46600000000014</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -674,14 +671,14 @@
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="12">
         <v>15</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21">
-        <v>32.041999999996946</v>
+      <c r="F4" s="20">
+        <v>130.34200000000001</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>19</v>
@@ -697,13 +694,13 @@
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="12">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <v>42.287000000000432</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -720,13 +717,13 @@
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="12">
         <v>26.18</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>69.795999999999992</v>
       </c>
       <c r="G6" s="8" t="s">
